--- a/outputs/monitor_xlsx/20260121.xlsx
+++ b/outputs/monitor_xlsx/20260121.xlsx
@@ -481,6 +481,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -823,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -878,6 +880,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -999,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1113,40 +1116,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1172,12 +1170,7 @@
       <c r="M4" t="n">
         <v>41754</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1203,12 +1196,7 @@
       <c r="M5" t="n">
         <v>34037</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1234,12 +1222,7 @@
       <c r="M6" t="n">
         <v>18044</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1265,12 +1248,7 @@
       <c r="M7" t="n">
         <v>37582</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1296,12 +1274,7 @@
       <c r="M8" t="n">
         <v>112020</v>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1327,12 +1300,7 @@
       <c r="M9" t="n">
         <v>657633</v>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1358,12 +1326,7 @@
       <c r="M10" t="n">
         <v>13801</v>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1389,12 +1352,7 @@
       <c r="M11" t="n">
         <v>27539</v>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1420,12 +1378,7 @@
       <c r="M12" t="n">
         <v>27700</v>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1451,12 +1404,7 @@
       <c r="M13" t="n">
         <v>787</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1482,12 +1430,7 @@
       <c r="M14" t="n">
         <v>-1480</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1513,12 +1456,7 @@
       <c r="M15" t="n">
         <v>1303</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1544,12 +1482,7 @@
       <c r="M16" t="n">
         <v>-896</v>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1575,12 +1508,7 @@
       <c r="M17" t="n">
         <v>47</v>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1606,12 +1534,7 @@
       <c r="M18" t="n">
         <v>12248</v>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1669,12 +1592,7 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1700,12 +1618,7 @@
       <c r="M20" t="n">
         <v>-671</v>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/outputs/monitor_xlsx/20260121.xlsx
+++ b/outputs/monitor_xlsx/20260121.xlsx
@@ -481,7 +481,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -824,7 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -880,7 +878,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1002,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1158,17 +1155,49 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
-        </is>
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>71.84999999999999</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>173683</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>-56688</v>
       </c>
       <c r="H4" t="n">
-        <v>-84736</v>
+        <v>-152462</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5000</v>
       </c>
       <c r="J4" t="n">
-        <v>5413</v>
+        <v>-5307</v>
+      </c>
+      <c r="K4" t="n">
+        <v>65125</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8010</v>
       </c>
       <c r="M4" t="n">
-        <v>41754</v>
+        <v>38917</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-3915625</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.99</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1213,14 +1242,46 @@
           <t>華城</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>1025</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>7506</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>348</v>
+      </c>
       <c r="H6" t="n">
-        <v>6342</v>
+        <v>2410</v>
+      </c>
+      <c r="I6" t="n">
+        <v>104</v>
       </c>
       <c r="J6" t="n">
-        <v>1111</v>
+        <v>1131</v>
+      </c>
+      <c r="K6" t="n">
+        <v>164</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2917</v>
       </c>
       <c r="M6" t="n">
-        <v>18044</v>
+        <v>15793</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-78581</v>
+      </c>
+      <c r="O6" t="n">
+        <v>15.07</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1239,14 +1300,46 @@
           <t>台達電</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>1135</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>18878</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>2395</v>
+      </c>
       <c r="H7" t="n">
-        <v>3300</v>
+        <v>6572</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-315</v>
       </c>
       <c r="J7" t="n">
-        <v>668</v>
+        <v>-90</v>
+      </c>
+      <c r="K7" t="n">
+        <v>421</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8402</v>
       </c>
       <c r="M7" t="n">
-        <v>37582</v>
+        <v>41975</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-648567</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5.83</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1265,14 +1358,46 @@
           <t>台積電</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>1740</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>50745</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>-18029</v>
+      </c>
       <c r="H8" t="n">
-        <v>-40987</v>
+        <v>-31688</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-3633</v>
       </c>
       <c r="J8" t="n">
-        <v>1891</v>
+        <v>-3229</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1765</v>
+      </c>
+      <c r="L8" t="n">
+        <v>21739</v>
       </c>
       <c r="M8" t="n">
-        <v>112020</v>
+        <v>106764</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-6482768</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.28</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1317,14 +1442,46 @@
           <t>台光電</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1560</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>-3.41</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>3510</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>356</v>
+      </c>
       <c r="H10" t="n">
-        <v>341</v>
+        <v>871</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-482</v>
       </c>
       <c r="J10" t="n">
-        <v>-708</v>
+        <v>-1518</v>
+      </c>
+      <c r="K10" t="n">
+        <v>206</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2326</v>
       </c>
       <c r="M10" t="n">
-        <v>13801</v>
+        <v>12625</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-89502</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-2.35</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1369,14 +1526,46 @@
           <t>光聖</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>4650</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>92</v>
+      </c>
       <c r="H12" t="n">
-        <v>-853</v>
+        <v>-587</v>
+      </c>
+      <c r="I12" t="n">
+        <v>81</v>
       </c>
       <c r="J12" t="n">
-        <v>-36</v>
+        <v>-131</v>
+      </c>
+      <c r="K12" t="n">
+        <v>115</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5211</v>
       </c>
       <c r="M12" t="n">
-        <v>27700</v>
+        <v>26705</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-19177</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-5.12</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1395,14 +1584,46 @@
           <t>聯亞</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>2365</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2182</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>916</v>
+      </c>
       <c r="H13" t="n">
-        <v>-1154</v>
+        <v>1362</v>
+      </c>
+      <c r="I13" t="n">
+        <v>443</v>
       </c>
       <c r="J13" t="n">
-        <v>180</v>
+        <v>668</v>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-325</v>
       </c>
       <c r="M13" t="n">
-        <v>787</v>
+        <v>-493</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1473,14 +1694,46 @@
           <t>華星光</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>586</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>32773</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>-2600</v>
+      </c>
       <c r="H16" t="n">
-        <v>-6057</v>
+        <v>-2594</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4100</v>
       </c>
       <c r="J16" t="n">
-        <v>-3523</v>
+        <v>2480</v>
+      </c>
+      <c r="K16" t="n">
+        <v>102</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-984</v>
       </c>
       <c r="M16" t="n">
-        <v>-896</v>
+        <v>-297</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1551,46 +1804,46 @@
           <t>智邦</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
         <v>1150</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="E19" s="6" t="n">
         <v>-2.95</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" s="6" t="n">
         <v>3893</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="6" t="n">
         <v>830</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>2600</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>-372</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>-677</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>324</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>2462</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>12747</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>-140152</v>
       </c>
-      <c r="N19" t="n">
-        <v>-3.87</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
+      <c r="O19" t="n">
+        <v>-4.56</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -1662,46 +1915,46 @@
           <t>均華</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>962</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>826</v>
+        <v>1625</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>-6.07</v>
       </c>
       <c r="F22" s="7" t="n">
+        <v>1168</v>
+      </c>
+      <c r="G22" s="7" t="n">
         <v>-34</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>-103</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>-5</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>-8</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>18</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>-9</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>-170</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
+      <c r="O22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1755,6 +2008,218 @@
         <is>
           <t>偏空</t>
         </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>995</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>3565</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2875</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-54</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1348</v>
+      </c>
+      <c r="K24" t="n">
+        <v>101</v>
+      </c>
+      <c r="L24" t="n">
+        <v>864</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4535</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-106259</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>3825</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>693</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="H25" t="n">
+        <v>86</v>
+      </c>
+      <c r="I25" t="n">
+        <v>24</v>
+      </c>
+      <c r="J25" t="n">
+        <v>231</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4</v>
+      </c>
+      <c r="L25" t="n">
+        <v>367</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2196</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-8861</v>
+      </c>
+      <c r="O25" t="n">
+        <v>9.01</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>6341</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>878</v>
+      </c>
+      <c r="H26" t="n">
+        <v>536</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>46</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-99</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-128</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>219</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>4662</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>-1344</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-2411</v>
+      </c>
+      <c r="I27" t="n">
+        <v>32</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-1156</v>
+      </c>
+      <c r="K27" t="n">
+        <v>64</v>
+      </c>
+      <c r="L27" t="n">
+        <v>6601</v>
+      </c>
+      <c r="M27" t="n">
+        <v>33664</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-21400</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-3.1</v>
       </c>
     </row>
   </sheetData>
